--- a/Reporte_gastos/tabla_gastos_zonas_2026-4.xlsx
+++ b/Reporte_gastos/tabla_gastos_zonas_2026-4.xlsx
@@ -538,7 +538,7 @@
         <v>1221357.44</v>
       </c>
       <c r="G6" t="n">
-        <v>490093.31</v>
+        <v>570093.31</v>
       </c>
     </row>
     <row r="7">
@@ -561,7 +561,7 @@
         <v>4132763.07</v>
       </c>
       <c r="G7" t="n">
-        <v>919161.06</v>
+        <v>999161.06</v>
       </c>
     </row>
     <row r="8">
@@ -584,7 +584,7 @@
         <v>1043217.11</v>
       </c>
       <c r="G8" t="n">
-        <v>312449.9</v>
+        <v>392449.9</v>
       </c>
     </row>
     <row r="9">
@@ -630,7 +630,7 @@
         <v>2945229.98</v>
       </c>
       <c r="G10" t="n">
-        <v>591580.9</v>
+        <v>671580.9</v>
       </c>
     </row>
     <row r="11">
@@ -653,7 +653,7 @@
         <v>586880.14</v>
       </c>
       <c r="G11" t="n">
-        <v>1650911.88</v>
+        <v>43711.8799999999</v>
       </c>
     </row>
     <row r="12">
@@ -699,7 +699,7 @@
         <v>2632798.19029</v>
       </c>
       <c r="G13" t="n">
-        <v>1694982.8</v>
+        <v>87782.7999999999</v>
       </c>
     </row>
     <row r="14">
@@ -722,7 +722,7 @@
         <v>2433399.73</v>
       </c>
       <c r="G14" t="n">
-        <v>2995123.8</v>
+        <v>414323.8</v>
       </c>
     </row>
     <row r="15">
@@ -745,7 +745,7 @@
         <v>24381710.71029</v>
       </c>
       <c r="G15" t="n">
-        <v>8789041.91</v>
+        <v>4761041.91</v>
       </c>
     </row>
   </sheetData>

--- a/Reporte_gastos/tabla_gastos_zonas_2026-4.xlsx
+++ b/Reporte_gastos/tabla_gastos_zonas_2026-4.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">TIENDA</t>
   </si>
@@ -21,6 +21,15 @@
   </si>
   <si>
     <t xml:space="preserve">Sueldos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incentivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribuciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total_sueldos</t>
   </si>
   <si>
     <t xml:space="preserve">Alquileres</t>
@@ -425,326 +434,461 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="n">
         <v>50187137.29</v>
       </c>
       <c r="C2" t="n">
+        <v>3859752.32360518</v>
+      </c>
+      <c r="D2" t="n">
+        <v>134200</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1167655.11624011</v>
+      </c>
+      <c r="F2" t="n">
         <v>5161607.4398453</v>
       </c>
-      <c r="D2" t="n">
+      <c r="G2" t="n">
         <v>6900000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="H2" t="n">
         <v>482850.5</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>7382850.5</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>2231609.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" t="n">
         <v>20708446.32</v>
       </c>
       <c r="C3" t="n">
+        <v>2850575.39166667</v>
+      </c>
+      <c r="D3" t="n">
+        <v>150483</v>
+      </c>
+      <c r="E3" t="n">
+        <v>888293.704468833</v>
+      </c>
+      <c r="F3" t="n">
         <v>3889352.0961355</v>
       </c>
-      <c r="D3" t="n">
+      <c r="G3" t="n">
         <v>2504086.52</v>
       </c>
-      <c r="E3" t="n">
+      <c r="H3" t="n">
         <v>2350582.72</v>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>4854669.24</v>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>356583.36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" t="n">
         <v>70895583.61</v>
       </c>
       <c r="C4" t="n">
+        <v>6710327.71527185</v>
+      </c>
+      <c r="D4" t="n">
+        <v>284683</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2055948.82070895</v>
+      </c>
+      <c r="F4" t="n">
         <v>9050959.53598079</v>
       </c>
-      <c r="D4" t="n">
+      <c r="G4" t="n">
         <v>9404086.52</v>
       </c>
-      <c r="E4" t="n">
+      <c r="H4" t="n">
         <v>2833433.22</v>
       </c>
-      <c r="F4" t="n">
+      <c r="I4" t="n">
         <v>12237519.74</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>2588193.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
         <v>31099293.12</v>
       </c>
       <c r="C5" t="n">
+        <v>2906030.53</v>
+      </c>
+      <c r="D5" t="n">
+        <v>165269</v>
+      </c>
+      <c r="E5" t="n">
+        <v>906540.46718</v>
+      </c>
+      <c r="F5" t="n">
         <v>3977839.99718</v>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" t="n">
         <v>2239640.96</v>
       </c>
-      <c r="E5" t="n">
+      <c r="H5" t="n">
         <v>671764.67</v>
       </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
         <v>2911405.63</v>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>429067.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6" t="n">
         <v>15741035.33</v>
       </c>
       <c r="C6" t="n">
+        <v>2338479.68258447</v>
+      </c>
+      <c r="D6" t="n">
+        <v>109721</v>
+      </c>
+      <c r="E6" t="n">
+        <v>718487.484640643</v>
+      </c>
+      <c r="F6" t="n">
         <v>3166688.16722511</v>
       </c>
-      <c r="D6" t="n">
+      <c r="G6" t="n">
         <v>923100</v>
       </c>
-      <c r="E6" t="n">
+      <c r="H6" t="n">
         <v>298257.44</v>
       </c>
-      <c r="F6" t="n">
+      <c r="I6" t="n">
         <v>1221357.44</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>570093.31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" t="n">
         <v>46840328.45</v>
       </c>
       <c r="C7" t="n">
+        <v>5244510.21258447</v>
+      </c>
+      <c r="D7" t="n">
+        <v>274990</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1625027.95182064</v>
+      </c>
+      <c r="F7" t="n">
         <v>7144528.16440511</v>
       </c>
-      <c r="D7" t="n">
+      <c r="G7" t="n">
         <v>3162740.96</v>
       </c>
-      <c r="E7" t="n">
+      <c r="H7" t="n">
         <v>970022.11</v>
       </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
         <v>4132763.07</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>999161.06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B8" t="n">
         <v>3226471.89</v>
       </c>
       <c r="C8" t="n">
+        <v>1241524.2174238</v>
+      </c>
+      <c r="D8" t="n">
+        <v>46498</v>
+      </c>
+      <c r="E8" t="n">
+        <v>377134.31348081</v>
+      </c>
+      <c r="F8" t="n">
         <v>1665156.53090461</v>
       </c>
-      <c r="D8" t="n">
+      <c r="G8" t="n">
         <v>715965.54</v>
       </c>
-      <c r="E8" t="n">
+      <c r="H8" t="n">
         <v>327251.57</v>
       </c>
-      <c r="F8" t="n">
+      <c r="I8" t="n">
         <v>1043217.11</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>392449.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B9" t="n">
         <v>10134262.01</v>
       </c>
       <c r="C9" t="n">
+        <v>2255698.42741553</v>
+      </c>
+      <c r="D9" t="n">
+        <v>51959</v>
+      </c>
+      <c r="E9" t="n">
+        <v>679425.847399357</v>
+      </c>
+      <c r="F9" t="n">
         <v>2987083.27481489</v>
       </c>
-      <c r="D9" t="n">
+      <c r="G9" t="n">
         <v>1230248.2</v>
       </c>
-      <c r="E9" t="n">
+      <c r="H9" t="n">
         <v>671764.67</v>
       </c>
-      <c r="F9" t="n">
+      <c r="I9" t="n">
         <v>1902012.87</v>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>279131</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B10" t="n">
         <v>13360733.9</v>
       </c>
       <c r="C10" t="n">
+        <v>3497222.64483934</v>
+      </c>
+      <c r="D10" t="n">
+        <v>98457</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1056560.16088017</v>
+      </c>
+      <c r="F10" t="n">
         <v>4652239.8057195</v>
       </c>
-      <c r="D10" t="n">
+      <c r="G10" t="n">
         <v>1946213.74</v>
       </c>
-      <c r="E10" t="n">
+      <c r="H10" t="n">
         <v>999016.24</v>
       </c>
-      <c r="F10" t="n">
+      <c r="I10" t="n">
         <v>2945229.98</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>671580.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>7638188.18</v>
       </c>
       <c r="C11" t="n">
+        <v>1932173.8384697</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3940</v>
+      </c>
+      <c r="E11" t="n">
+        <v>549433.974881397</v>
+      </c>
+      <c r="F11" t="n">
         <v>2485547.81335109</v>
       </c>
-      <c r="D11" t="n">
+      <c r="G11" t="n">
         <v>536812.83</v>
       </c>
-      <c r="E11" t="n">
+      <c r="H11" t="n">
         <v>50067.31</v>
       </c>
-      <c r="F11" t="n">
+      <c r="I11" t="n">
         <v>586880.14</v>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>43711.8799999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>10038251.16</v>
       </c>
       <c r="C12" t="n">
+        <v>3268069.81883465</v>
+      </c>
+      <c r="D12" t="n">
+        <v>65014</v>
+      </c>
+      <c r="E12" t="n">
+        <v>972332.642358846</v>
+      </c>
+      <c r="F12" t="n">
         <v>4305416.4611935</v>
       </c>
-      <c r="D12" t="n">
+      <c r="G12" t="n">
         <v>1872828.43029</v>
       </c>
-      <c r="E12" t="n">
+      <c r="H12" t="n">
         <v>173089.62</v>
       </c>
-      <c r="F12" t="n">
+      <c r="I12" t="n">
         <v>2045918.05029</v>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
         <v>44070.92</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B13" t="n">
         <v>17676439.34</v>
       </c>
       <c r="C13" t="n">
+        <v>5200243.65730435</v>
+      </c>
+      <c r="D13" t="n">
+        <v>68954</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1521766.61724024</v>
+      </c>
+      <c r="F13" t="n">
         <v>6790964.27454459</v>
       </c>
-      <c r="D13" t="n">
+      <c r="G13" t="n">
         <v>2409641.26029</v>
       </c>
-      <c r="E13" t="n">
+      <c r="H13" t="n">
         <v>223156.93</v>
       </c>
-      <c r="F13" t="n">
+      <c r="I13" t="n">
         <v>2632798.19029</v>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>87782.7999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14" t="n">
         <v>14072096.39</v>
       </c>
       <c r="C14" t="n">
+        <v>2655638.1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>79855</v>
+      </c>
+      <c r="E14" t="n">
+        <v>802771.326555</v>
+      </c>
+      <c r="F14" t="n">
         <v>3538264.426555</v>
       </c>
-      <c r="D14" t="n">
+      <c r="G14" t="n">
         <v>1089870.39</v>
       </c>
-      <c r="E14" t="n">
+      <c r="H14" t="n">
         <v>1343529.34</v>
       </c>
-      <c r="F14" t="n">
+      <c r="I14" t="n">
         <v>2433399.73</v>
       </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
         <v>414323.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B15" t="n">
         <v>162845181.69</v>
       </c>
       <c r="C15" t="n">
+        <v>23307942.33</v>
+      </c>
+      <c r="D15" t="n">
+        <v>806939</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7062074.877205</v>
+      </c>
+      <c r="F15" t="n">
         <v>31176956.207205</v>
       </c>
-      <c r="D15" t="n">
+      <c r="G15" t="n">
         <v>18012552.87029</v>
       </c>
-      <c r="E15" t="n">
+      <c r="H15" t="n">
         <v>6369157.84</v>
       </c>
-      <c r="F15" t="n">
+      <c r="I15" t="n">
         <v>24381710.71029</v>
       </c>
-      <c r="G15" t="n">
+      <c r="J15" t="n">
         <v>4761041.91</v>
       </c>
     </row>
